--- a/contents/files/5_邏輯函數組合應用.xlsx
+++ b/contents/files/5_邏輯函數組合應用.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shelf\Lecture\114.2 電腦軟體應用\Hello Excel\contents\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78361A99-2B55-4FCE-A56A-22A6D8735404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EA5C97-01BB-4AC0-B3F6-68B883FB8D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9495" yWindow="0" windowWidth="9810" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="邏輯函數練習" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="34">
   <si>
     <t>邏輯函數組合應用練習</t>
   </si>
@@ -122,12 +135,6 @@
   </si>
   <si>
     <t>XOR 結果</t>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>FALSE</t>
   </si>
 </sst>
 </file>
@@ -147,22 +154,26 @@
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF375623"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -245,12 +256,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -567,24 +578,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="3" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -665,14 +676,14 @@
       <c r="D9" s="4"/>
     </row>
     <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -753,14 +764,14 @@
       <c r="D18" s="4"/>
     </row>
     <row r="21" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -858,14 +869,14 @@
       <c r="E27" s="4"/>
     </row>
     <row r="30" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -929,14 +940,14 @@
       <c r="C36" s="4"/>
     </row>
     <row r="39" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
     </row>
     <row r="40" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -960,11 +971,11 @@
       <c r="A41" s="2">
         <v>1</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>35</v>
+      <c r="B41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C41" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="D41" s="4"/>
     </row>
@@ -972,11 +983,11 @@
       <c r="A42" s="2">
         <v>2</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>34</v>
+      <c r="B42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C42" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="D42" s="4"/>
     </row>
@@ -984,11 +995,11 @@
       <c r="A43" s="2">
         <v>3</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>34</v>
+      <c r="B43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="D43" s="4"/>
     </row>
@@ -996,11 +1007,11 @@
       <c r="A44" s="2">
         <v>4</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>35</v>
+      <c r="B44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C44" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="D44" s="4"/>
     </row>
@@ -1008,22 +1019,22 @@
       <c r="A45" s="2">
         <v>5</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>35</v>
+      <c r="B45" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="D45" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
